--- a/inst/cprd/ons_dd.xlsx
+++ b/inst/cprd/ons_dd.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">%Y%m%d</t>
+    <t xml:space="preserve">%Y-%m-%d</t>
   </si>
   <si>
     <t xml:space="preserve">reg_date_of_death</t>
@@ -328,34 +328,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -501,9 +501,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="45.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="1" width="11.53"/>
   </cols>
@@ -536,7 +536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="31.3" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -550,7 +550,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -564,7 +564,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -606,7 +606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -620,7 +620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -634,7 +634,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
@@ -648,7 +648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -662,7 +662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -676,7 +676,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -690,7 +690,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -704,7 +704,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -718,7 +718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
         <v>35</v>
       </c>
@@ -732,7 +732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
@@ -746,7 +746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
         <v>37</v>
       </c>
@@ -760,7 +760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
         <v>38</v>
       </c>
@@ -774,7 +774,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
@@ -788,7 +788,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
@@ -802,7 +802,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
         <v>41</v>
       </c>
@@ -816,7 +816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
         <v>42</v>
       </c>
@@ -830,7 +830,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>43</v>
       </c>
@@ -844,7 +844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>45</v>
       </c>
@@ -858,7 +858,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>46</v>
       </c>
@@ -872,7 +872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
@@ -886,7 +886,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
@@ -900,7 +900,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>49</v>
       </c>
@@ -914,7 +914,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>50</v>
       </c>
@@ -928,7 +928,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
@@ -942,7 +942,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
@@ -956,7 +956,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
@@ -970,7 +970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>54</v>
       </c>
@@ -984,7 +984,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
@@ -998,7 +998,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>56</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>57</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>58</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>61</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
         <v>63</v>
       </c>
